--- a/virtual-physics-lab/app/dl/DHS_Q3_bifilar.xlsx
+++ b/virtual-physics-lab/app/dl/DHS_Q3_bifilar.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <name val="Calibri"/>
@@ -91,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -99,9 +101,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -684,87 +688,87 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>6.97</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>6.98</v>
-      </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>8.32</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>8.369999999999999</v>
-      </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>10.21</v>
-      </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>12.24</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>12.28</v>
-      </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>14.63</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>14.56</v>
-      </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>17.02</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>17.07</v>
-      </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>15.82</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>15.86</v>
+      </c>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -854,36 +858,36 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>6.97</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>6.98</v>
-      </c>
-      <c r="D6" s="7">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="D6" s="8">
         <f>(B6+C6)/20</f>
         <v/>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="8">
         <f>D6^2</f>
         <v/>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="8">
         <f>(A6/100)^2</f>
         <v/>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>gradient</t>
         </is>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="8">
         <f>SLOPE(E6:E11,F6:F11)</f>
         <v/>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>s² m⁻²</t>
         </is>
@@ -891,36 +895,36 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>8.32</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>8.369999999999999</v>
-      </c>
-      <c r="D7" s="7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="D7" s="8">
         <f>(B7+C7)/20</f>
         <v/>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="8">
         <f>D7^2</f>
         <v/>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="8">
         <f>(A7/100)^2</f>
         <v/>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t>C = intercept</t>
         </is>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="8">
         <f>INTERCEPT(E6:E11,F6:F11)</f>
         <v/>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>s²</t>
         </is>
@@ -928,36 +932,36 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>10.21</v>
-      </c>
-      <c r="D8" s="7">
+        <v>9</v>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="D8" s="8">
         <f>(B8+C8)/20</f>
         <v/>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <f>D8^2</f>
         <v/>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="8">
         <f>(A8/100)^2</f>
         <v/>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="9" t="inlineStr">
         <is>
           <t>I₀ = CMgd²/(4π²l)</t>
         </is>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="8">
         <f>INTERCEPT(E6:E11,F6:F11)*0.1462*9.81*0.3^2/(4*PI()^2*0.351)</f>
         <v/>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>kg m²</t>
         </is>
@@ -965,69 +969,69 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>12.24</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>12.28</v>
-      </c>
-      <c r="D9" s="7">
+        <v>12</v>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="D9" s="8">
         <f>(B9+C9)/20</f>
         <v/>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="8">
         <f>D9^2</f>
         <v/>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="8">
         <f>(A9/100)^2</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>14.63</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>14.56</v>
-      </c>
-      <c r="D10" s="7">
+        <v>19</v>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="D10" s="8">
         <f>(B10+C10)/20</f>
         <v/>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="8">
         <f>D10^2</f>
         <v/>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="8">
         <f>(A10/100)^2</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>17.02</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>17.07</v>
-      </c>
-      <c r="D11" s="7">
+        <v>22</v>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>15.82</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>15.86</v>
+      </c>
+      <c r="D11" s="8">
         <f>(B11+C11)/20</f>
         <v/>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="8">
         <f>D11^2</f>
         <v/>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="8">
         <f>(A11/100)^2</f>
         <v/>
       </c>
